--- a/artfynd/A 16920-2024 artfynd.xlsx
+++ b/artfynd/A 16920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117753482</v>
+        <v>117753479</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422271</v>
+        <v>422239</v>
       </c>
       <c r="R2" t="n">
-        <v>7043943</v>
+        <v>7043838</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117753475</v>
+        <v>117753460</v>
       </c>
       <c r="B3" t="n">
-        <v>57398</v>
+        <v>90499</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,54 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kroksvalen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422124</v>
+        <v>422291</v>
       </c>
       <c r="R3" t="n">
-        <v>7043935</v>
+        <v>7043885</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117753479</v>
+        <v>117753467</v>
       </c>
       <c r="B4" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422239</v>
+        <v>422269</v>
       </c>
       <c r="R4" t="n">
-        <v>7043838</v>
+        <v>7043780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117753467</v>
+        <v>117753482</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422269</v>
+        <v>422271</v>
       </c>
       <c r="R5" t="n">
-        <v>7043780</v>
+        <v>7043943</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117753460</v>
+        <v>117753475</v>
       </c>
       <c r="B6" t="n">
-        <v>90499</v>
+        <v>57398</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,38 +1105,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kroksvalen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422291</v>
+        <v>422124</v>
       </c>
       <c r="R6" t="n">
-        <v>7043885</v>
+        <v>7043935</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 16920-2024 artfynd.xlsx
+++ b/artfynd/A 16920-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117753479</v>
+        <v>117753467</v>
       </c>
       <c r="B2" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422239</v>
+        <v>422269</v>
       </c>
       <c r="R2" t="n">
-        <v>7043838</v>
+        <v>7043780</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117753460</v>
+        <v>117753475</v>
       </c>
       <c r="B3" t="n">
-        <v>90499</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +794,54 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kroksvalen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422291</v>
+        <v>422124</v>
       </c>
       <c r="R3" t="n">
-        <v>7043885</v>
+        <v>7043935</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117753467</v>
+        <v>117753482</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422269</v>
+        <v>422271</v>
       </c>
       <c r="R4" t="n">
-        <v>7043780</v>
+        <v>7043943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +980,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117753482</v>
+        <v>117753460</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422271</v>
+        <v>422291</v>
       </c>
       <c r="R5" t="n">
-        <v>7043943</v>
+        <v>7043885</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1083,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117753475</v>
+        <v>117753479</v>
       </c>
       <c r="B6" t="n">
-        <v>57398</v>
+        <v>90519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,54 +1121,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kroksvalen Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422124</v>
+        <v>422239</v>
       </c>
       <c r="R6" t="n">
-        <v>7043935</v>
+        <v>7043838</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
